--- a/artfynd/A 49089-2025 artfynd.xlsx
+++ b/artfynd/A 49089-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>129561070</v>
       </c>
       <c r="B2" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -769,6 +769,431 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>129584830</v>
+      </c>
+      <c r="B3" t="n">
+        <v>98727</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Eketorpet, Eketorpet, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>581595</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6326732</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129581895</v>
+      </c>
+      <c r="B4" t="n">
+        <v>97598</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Eketorpet, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>581595</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6326732</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129585791</v>
+      </c>
+      <c r="B5" t="n">
+        <v>92206</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6031</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Sparassis crispa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Eketorpet, Eketorpet, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>581595</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6326732</v>
+      </c>
+      <c r="S5" t="n">
+        <v>20</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129585930</v>
+      </c>
+      <c r="B6" t="n">
+        <v>105793</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Eketorpet, Eketorpet, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>581595</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6326732</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 49089-2025 artfynd.xlsx
+++ b/artfynd/A 49089-2025 artfynd.xlsx
@@ -883,10 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129581895</v>
+        <v>129585791</v>
       </c>
       <c r="B4" t="n">
-        <v>97598</v>
+        <v>92206</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -894,27 +894,36 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>6031</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Eketorpet, Sm</t>
+          <t>Eketorpet, Eketorpet, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
@@ -924,7 +933,7 @@
         <v>6326732</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -980,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129585791</v>
+        <v>129581895</v>
       </c>
       <c r="B5" t="n">
-        <v>92206</v>
+        <v>97598</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -991,36 +1000,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6031</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Eketorpet, Eketorpet, Sm</t>
+          <t>Eketorpet, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
@@ -1030,7 +1030,7 @@
         <v>6326732</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>

--- a/artfynd/A 49089-2025 artfynd.xlsx
+++ b/artfynd/A 49089-2025 artfynd.xlsx
@@ -921,6 +921,8 @@
           <t>bålar</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Eketorpet, Eketorpet, Sm</t>
@@ -971,6 +973,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 49089-2025 artfynd.xlsx
+++ b/artfynd/A 49089-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129561070</v>
       </c>
       <c r="B2" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129584830</v>
       </c>
       <c r="B3" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -883,10 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129585791</v>
+        <v>129581895</v>
       </c>
       <c r="B4" t="n">
-        <v>92206</v>
+        <v>97627</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -894,38 +894,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6031</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Eketorpet, Eketorpet, Sm</t>
+          <t>Eketorpet, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
@@ -935,7 +924,7 @@
         <v>6326732</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -973,7 +962,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -992,10 +980,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129581895</v>
+        <v>129585791</v>
       </c>
       <c r="B5" t="n">
-        <v>97598</v>
+        <v>92234</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1003,27 +991,38 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>6031</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Eketorpet, Sm</t>
+          <t>Eketorpet, Eketorpet, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
@@ -1033,7 +1032,7 @@
         <v>6326732</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1071,6 +1070,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1092,7 +1092,7 @@
         <v>129585930</v>
       </c>
       <c r="B6" t="n">
-        <v>105793</v>
+        <v>105822</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 49089-2025 artfynd.xlsx
+++ b/artfynd/A 49089-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129561070</v>
       </c>
       <c r="B2" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129584830</v>
       </c>
       <c r="B3" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -883,10 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129581895</v>
+        <v>129585791</v>
       </c>
       <c r="B4" t="n">
-        <v>97627</v>
+        <v>92240</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -894,27 +894,38 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>6031</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Eketorpet, Sm</t>
+          <t>Eketorpet, Eketorpet, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
@@ -924,7 +935,7 @@
         <v>6326732</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -962,6 +973,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -980,10 +992,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129585791</v>
+        <v>129581895</v>
       </c>
       <c r="B5" t="n">
-        <v>92234</v>
+        <v>97639</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -991,38 +1003,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6031</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Eketorpet, Eketorpet, Sm</t>
+          <t>Eketorpet, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
@@ -1032,7 +1033,7 @@
         <v>6326732</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1070,7 +1071,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1092,7 +1092,7 @@
         <v>129585930</v>
       </c>
       <c r="B6" t="n">
-        <v>105822</v>
+        <v>105834</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 49089-2025 artfynd.xlsx
+++ b/artfynd/A 49089-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129561070</v>
       </c>
       <c r="B2" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129584830</v>
       </c>
       <c r="B3" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -883,10 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129585791</v>
+        <v>129581895</v>
       </c>
       <c r="B4" t="n">
-        <v>92240</v>
+        <v>97640</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -894,38 +894,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6031</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Eketorpet, Eketorpet, Sm</t>
+          <t>Eketorpet, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
@@ -935,7 +924,7 @@
         <v>6326732</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -973,7 +962,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -992,10 +980,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129581895</v>
+        <v>129585791</v>
       </c>
       <c r="B5" t="n">
-        <v>97639</v>
+        <v>92241</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1003,27 +991,38 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>6031</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Eketorpet, Sm</t>
+          <t>Eketorpet, Eketorpet, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
@@ -1033,7 +1032,7 @@
         <v>6326732</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1071,6 +1070,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1092,7 +1092,7 @@
         <v>129585930</v>
       </c>
       <c r="B6" t="n">
-        <v>105834</v>
+        <v>105835</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 49089-2025 artfynd.xlsx
+++ b/artfynd/A 49089-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129561070</v>
       </c>
       <c r="B2" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129584830</v>
       </c>
       <c r="B3" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>129581895</v>
       </c>
       <c r="B4" t="n">
-        <v>97640</v>
+        <v>97645</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
         <v>129585791</v>
       </c>
       <c r="B5" t="n">
-        <v>92241</v>
+        <v>92246</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>129585930</v>
       </c>
       <c r="B6" t="n">
-        <v>105835</v>
+        <v>105840</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 49089-2025 artfynd.xlsx
+++ b/artfynd/A 49089-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -769,434 +769,6 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>129584830</v>
-      </c>
-      <c r="B3" t="n">
-        <v>98774</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Eketorpet, Eketorpet, Sm</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>581595</v>
-      </c>
-      <c r="R3" t="n">
-        <v>6326732</v>
-      </c>
-      <c r="S3" t="n">
-        <v>10</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Mönsterås</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Mönsterås</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2025-11-07</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2025-11-07</t>
-        </is>
-      </c>
-      <c r="AD3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>Lars Engström</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Lars Engström</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>129581895</v>
-      </c>
-      <c r="B4" t="n">
-        <v>97645</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>221945</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Eketorpet, Sm</t>
-        </is>
-      </c>
-      <c r="Q4" t="n">
-        <v>581595</v>
-      </c>
-      <c r="R4" t="n">
-        <v>6326732</v>
-      </c>
-      <c r="S4" t="n">
-        <v>10</v>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Mönsterås</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Mönsterås</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2025-11-07</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>2025-11-07</t>
-        </is>
-      </c>
-      <c r="AD4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>Lars Engström</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>Lars Engström</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>129585791</v>
-      </c>
-      <c r="B5" t="n">
-        <v>92246</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>6031</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Blomkålssvamp</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Sparassis crispa</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Wulfen:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Eketorpet, Eketorpet, Sm</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>581595</v>
-      </c>
-      <c r="R5" t="n">
-        <v>6326732</v>
-      </c>
-      <c r="S5" t="n">
-        <v>20</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Mönsterås</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Mönsterås</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2025-11-07</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2025-11-07</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Lars Engström</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Lars Engström</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>129585930</v>
-      </c>
-      <c r="B6" t="n">
-        <v>105840</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>221144</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Grönpyrola</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Pyrola chlorantha</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Eketorpet, Eketorpet, Sm</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>581595</v>
-      </c>
-      <c r="R6" t="n">
-        <v>6326732</v>
-      </c>
-      <c r="S6" t="n">
-        <v>10</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Mönsterås</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Mönsterås</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2025-11-07</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2025-11-07</t>
-        </is>
-      </c>
-      <c r="AD6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>Lars Engström</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>Lars Engström</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 49089-2025 artfynd.xlsx
+++ b/artfynd/A 49089-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129561070</v>
       </c>
       <c r="B2" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 49089-2025 artfynd.xlsx
+++ b/artfynd/A 49089-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129561070</v>
       </c>
       <c r="B2" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 49089-2025 artfynd.xlsx
+++ b/artfynd/A 49089-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129561070</v>
       </c>
       <c r="B2" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 49089-2025 artfynd.xlsx
+++ b/artfynd/A 49089-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129561070</v>
       </c>
       <c r="B2" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
